--- a/assets/constructions/examples/ctd_tge_arbor_module_holder.xlsx
+++ b/assets/constructions/examples/ctd_tge_arbor_module_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,11 +569,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VBC C5-00-C</t>
+          <t>VBCL C6-90-C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -588,7 +608,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_VBC5</t>
+          <t>VAR_VBC6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -598,7 +618,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ISO_26623:50</t>
+          <t>ISO_26623:63</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -607,7 +627,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -616,7 +636,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -626,19 +646,19 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>51.9</v>
+        <v>33.2</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -657,6 +677,20 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1184.93</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>108935</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -745,11 +779,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1093.78</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>100555.24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VBCL C4-90-C</t>
+          <t>VBC C5-00-C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -764,7 +812,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VAR_VBC4</t>
+          <t>VAR_VBC5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -774,7 +822,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ISO_26623:40</t>
+          <t>ISO_26623:50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -783,7 +831,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -792,7 +840,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -806,15 +854,15 @@
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>33</v>
+        <v>51.9</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -833,11 +881,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1177.48</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>108250.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VBCR C5-90-C</t>
+          <t>VBCL C5-90-C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -880,7 +942,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -921,11 +983,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1093.45</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>100524.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VBC C6-00-C</t>
+          <t>VBCR C5-90-C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -940,7 +1016,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VAR_VBC6</t>
+          <t>VAR_VBC5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -950,7 +1026,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ISO_26623:63</t>
+          <t>ISO_26623:50</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -959,7 +1035,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -968,7 +1044,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -978,19 +1054,19 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="R6" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>61.9</v>
+        <v>33.25</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1008,6 +1084,20 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1093.45</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>100524.9</v>
       </c>
     </row>
   </sheetData>
